--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221091</v>
+        <v>125221164</v>
       </c>
       <c r="B2" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518257</v>
+        <v>518209</v>
       </c>
       <c r="R2" t="n">
-        <v>6877809</v>
+        <v>6878040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221090</v>
+        <v>125221091</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518205</v>
+        <v>518257</v>
       </c>
       <c r="R3" t="n">
-        <v>6878025</v>
+        <v>6877809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221164</v>
+        <v>125221090</v>
       </c>
       <c r="B4" t="n">
         <v>79891</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518209</v>
+        <v>518205</v>
       </c>
       <c r="R4" t="n">
-        <v>6878040</v>
+        <v>6878025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221164</v>
+        <v>125221090</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518209</v>
+        <v>518205</v>
       </c>
       <c r="R2" t="n">
-        <v>6878040</v>
+        <v>6878025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221091</v>
+        <v>125221164</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518257</v>
+        <v>518209</v>
       </c>
       <c r="R3" t="n">
-        <v>6877809</v>
+        <v>6878040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221090</v>
+        <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518205</v>
+        <v>518257</v>
       </c>
       <c r="R4" t="n">
-        <v>6878025</v>
+        <v>6877809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221090</v>
+        <v>125221164</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518205</v>
+        <v>518209</v>
       </c>
       <c r="R2" t="n">
-        <v>6878025</v>
+        <v>6878040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221164</v>
+        <v>125221090</v>
       </c>
       <c r="B3" t="n">
         <v>79891</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518209</v>
+        <v>518205</v>
       </c>
       <c r="R3" t="n">
-        <v>6878040</v>
+        <v>6878025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221164</v>
+        <v>125221090</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518209</v>
+        <v>518205</v>
       </c>
       <c r="R2" t="n">
-        <v>6878040</v>
+        <v>6878025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221090</v>
+        <v>125221091</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518205</v>
+        <v>518257</v>
       </c>
       <c r="R3" t="n">
-        <v>6878025</v>
+        <v>6877809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221091</v>
+        <v>125221164</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518257</v>
+        <v>518209</v>
       </c>
       <c r="R4" t="n">
-        <v>6877809</v>
+        <v>6878040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221090</v>
+        <v>125221164</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518205</v>
+        <v>518209</v>
       </c>
       <c r="R2" t="n">
-        <v>6878025</v>
+        <v>6878040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221091</v>
+        <v>125221090</v>
       </c>
       <c r="B3" t="n">
-        <v>78546</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518257</v>
+        <v>518205</v>
       </c>
       <c r="R3" t="n">
-        <v>6877809</v>
+        <v>6878025</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221164</v>
+        <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518209</v>
+        <v>518257</v>
       </c>
       <c r="R4" t="n">
-        <v>6878040</v>
+        <v>6877809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221164</v>
+        <v>125221091</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>78683</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518209</v>
+        <v>518257</v>
       </c>
       <c r="R2" t="n">
-        <v>6878040</v>
+        <v>6877809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>125221090</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>80028</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221091</v>
+        <v>125221164</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518257</v>
+        <v>518209</v>
       </c>
       <c r="R4" t="n">
-        <v>6877809</v>
+        <v>6878040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125221091</v>
+        <v>125221090</v>
       </c>
       <c r="B2" t="n">
-        <v>78683</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518257</v>
+        <v>518205</v>
       </c>
       <c r="R2" t="n">
-        <v>6877809</v>
+        <v>6878025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125221090</v>
+        <v>125221164</v>
       </c>
       <c r="B3" t="n">
         <v>80028</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518205</v>
+        <v>518209</v>
       </c>
       <c r="R3" t="n">
-        <v>6878025</v>
+        <v>6878040</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125221164</v>
+        <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>78683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518209</v>
+        <v>518257</v>
       </c>
       <c r="R4" t="n">
-        <v>6878040</v>
+        <v>6877809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221090</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221164</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221090</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221164</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221090</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221164</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 18913-2020 artfynd.xlsx
+++ b/artfynd/A 18913-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125221090</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>125221164</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>125221091</v>
       </c>
       <c r="B4" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
